--- a/output/Tables/2019/Monte Carlo/HIA_per_age.xlsx
+++ b/output/Tables/2019/Monte Carlo/HIA_per_age.xlsx
@@ -438,22 +438,22 @@
         </is>
       </c>
       <c r="C2">
-        <v>449.477</v>
+        <v>448.754</v>
       </c>
       <c r="D2">
-        <v>404.594</v>
+        <v>403.952</v>
       </c>
       <c r="E2">
-        <v>494.376</v>
+        <v>493.54</v>
       </c>
       <c r="F2">
-        <v>25612.661</v>
+        <v>25654.969</v>
       </c>
       <c r="G2">
-        <v>23099.992</v>
+        <v>23137.893</v>
       </c>
       <c r="H2">
-        <v>28092.944</v>
+        <v>28176.161</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>3412723644.855</v>
+        <v>3411965857.546</v>
       </c>
       <c r="M2">
-        <v>3070922394.477</v>
+        <v>3076430845.945</v>
       </c>
       <c r="N2">
-        <v>3735885726.737</v>
+        <v>3747683723.574</v>
       </c>
     </row>
     <row r="3">
@@ -486,22 +486,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>860.902</v>
+        <v>862.462</v>
       </c>
       <c r="D3">
-        <v>785.89</v>
+        <v>785.526</v>
       </c>
       <c r="E3">
-        <v>935.9160000000001</v>
+        <v>939.177</v>
       </c>
       <c r="F3">
-        <v>40051.403</v>
+        <v>40141.257</v>
       </c>
       <c r="G3">
-        <v>36567.689</v>
+        <v>36701.424</v>
       </c>
       <c r="H3">
-        <v>43711.669</v>
+        <v>43590.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>5346828837.341</v>
+        <v>5338426878.719</v>
       </c>
       <c r="M3">
-        <v>4874691808.934</v>
+        <v>4879561227.011</v>
       </c>
       <c r="N3">
-        <v>5798239978.768</v>
+        <v>5799989066.212</v>
       </c>
     </row>
     <row r="4">
@@ -534,22 +534,22 @@
         </is>
       </c>
       <c r="C4">
-        <v>2287.269</v>
+        <v>2288.788</v>
       </c>
       <c r="D4">
-        <v>2092.715</v>
+        <v>2095.715</v>
       </c>
       <c r="E4">
-        <v>2476.788</v>
+        <v>2480.551</v>
       </c>
       <c r="F4">
-        <v>85045.102</v>
+        <v>84961.026</v>
       </c>
       <c r="G4">
-        <v>78286.466</v>
+        <v>77960.683</v>
       </c>
       <c r="H4">
-        <v>92095.78599999999</v>
+        <v>91969.166</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -561,13 +561,13 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>11280817610.353</v>
+        <v>11303408325.729</v>
       </c>
       <c r="M4">
-        <v>10368989460.043</v>
+        <v>10369275160.191</v>
       </c>
       <c r="N4">
-        <v>12251740644.363</v>
+        <v>12242616587.612</v>
       </c>
     </row>
     <row r="5">
@@ -582,22 +582,22 @@
         </is>
       </c>
       <c r="C5">
-        <v>4883.427</v>
+        <v>4887.26</v>
       </c>
       <c r="D5">
-        <v>4509.212</v>
+        <v>4508.786</v>
       </c>
       <c r="E5">
-        <v>5253.357</v>
+        <v>5268.88</v>
       </c>
       <c r="F5">
-        <v>131717.74</v>
+        <v>131611.25</v>
       </c>
       <c r="G5">
-        <v>121740.61</v>
+        <v>121833.737</v>
       </c>
       <c r="H5">
-        <v>141121.525</v>
+        <v>141380.902</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -609,13 +609,13 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>17490005354.426</v>
+        <v>17505177919.406</v>
       </c>
       <c r="M5">
-        <v>16253614259.397</v>
+        <v>16201162240.009</v>
       </c>
       <c r="N5">
-        <v>18800250651.188</v>
+        <v>18810827198.624</v>
       </c>
     </row>
     <row r="6">
@@ -630,22 +630,22 @@
         </is>
       </c>
       <c r="C6">
-        <v>10427.637</v>
+        <v>10426.459</v>
       </c>
       <c r="D6">
-        <v>9661.246999999999</v>
+        <v>9654.338</v>
       </c>
       <c r="E6">
-        <v>11202.46</v>
+        <v>11200.527</v>
       </c>
       <c r="F6">
-        <v>178309.209</v>
+        <v>178163.438</v>
       </c>
       <c r="G6">
-        <v>165781.161</v>
+        <v>165584.761</v>
       </c>
       <c r="H6">
-        <v>190643.838</v>
+        <v>190787.25</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -657,13 +657,13 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>23736238906.918</v>
+        <v>23696310362.035</v>
       </c>
       <c r="M6">
-        <v>22112146706.033</v>
+        <v>22021518575.122</v>
       </c>
       <c r="N6">
-        <v>25422515266.141</v>
+        <v>25372420292.966</v>
       </c>
     </row>
     <row r="7">
@@ -678,22 +678,22 @@
         </is>
       </c>
       <c r="C7">
-        <v>16807.838</v>
+        <v>16760.506</v>
       </c>
       <c r="D7">
-        <v>15421.944</v>
+        <v>15370.659</v>
       </c>
       <c r="E7">
-        <v>18228.153</v>
+        <v>18151.309</v>
       </c>
       <c r="F7">
-        <v>124750.431</v>
+        <v>124288.34</v>
       </c>
       <c r="G7">
-        <v>115204.681</v>
+        <v>115237.817</v>
       </c>
       <c r="H7">
-        <v>133730.58</v>
+        <v>133327.512</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>16568092674.436</v>
+        <v>16527494927.454</v>
       </c>
       <c r="M7">
-        <v>15391844749.385</v>
+        <v>15333039407.126</v>
       </c>
       <c r="N7">
-        <v>17759246769.973</v>
+        <v>17727583611.788</v>
       </c>
     </row>
     <row r="8">
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="C8">
-        <v>22837.646</v>
+        <v>22820.376</v>
       </c>
       <c r="D8">
-        <v>20320.905</v>
+        <v>20283.101</v>
       </c>
       <c r="E8">
-        <v>25443.004</v>
+        <v>25359.155</v>
       </c>
       <c r="F8">
-        <v>19983.71</v>
+        <v>19968.089</v>
       </c>
       <c r="G8">
-        <v>16771.144</v>
+        <v>16870.066</v>
       </c>
       <c r="H8">
-        <v>23043.454</v>
+        <v>23074.378</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -753,13 +753,13 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>2659428389.38</v>
+        <v>2655058613.693</v>
       </c>
       <c r="M8">
-        <v>2242629575.115</v>
+        <v>2243773621.972</v>
       </c>
       <c r="N8">
-        <v>3069889351.37</v>
+        <v>3068130030.275</v>
       </c>
     </row>
     <row r="9">
@@ -774,40 +774,40 @@
         </is>
       </c>
       <c r="C9">
-        <v>229.008</v>
+        <v>230.179</v>
       </c>
       <c r="D9">
-        <v>205.955</v>
+        <v>205.23</v>
       </c>
       <c r="E9">
-        <v>253.352</v>
+        <v>255.416</v>
       </c>
       <c r="F9">
-        <v>865.633</v>
+        <v>872.289</v>
       </c>
       <c r="G9">
-        <v>773.197</v>
+        <v>778.341</v>
       </c>
       <c r="H9">
-        <v>961.658</v>
+        <v>968.919</v>
       </c>
       <c r="I9">
-        <v>12775165.222</v>
+        <v>12818083.091</v>
       </c>
       <c r="J9">
-        <v>11467217.71</v>
+        <v>11436698.683</v>
       </c>
       <c r="K9">
-        <v>14163542.537</v>
+        <v>14222118.27</v>
       </c>
       <c r="L9">
-        <v>115643380.862</v>
+        <v>116007810.948</v>
       </c>
       <c r="M9">
-        <v>102737968.246</v>
+        <v>103478035.473</v>
       </c>
       <c r="N9">
-        <v>127826540.013</v>
+        <v>128826546.903</v>
       </c>
     </row>
     <row r="10">
@@ -822,40 +822,40 @@
         </is>
       </c>
       <c r="C10">
-        <v>480.458</v>
+        <v>479.633</v>
       </c>
       <c r="D10">
-        <v>434.209</v>
+        <v>433.222</v>
       </c>
       <c r="E10">
-        <v>529.649</v>
+        <v>526.566</v>
       </c>
       <c r="F10">
-        <v>1497.598</v>
+        <v>1499.014</v>
       </c>
       <c r="G10">
-        <v>1354.558</v>
+        <v>1354.43</v>
       </c>
       <c r="H10">
-        <v>1645.929</v>
+        <v>1646.415</v>
       </c>
       <c r="I10">
-        <v>26769811.841</v>
+        <v>26710382.684</v>
       </c>
       <c r="J10">
-        <v>24102156.71</v>
+        <v>24124674.183</v>
       </c>
       <c r="K10">
-        <v>29321271.945</v>
+        <v>29348738.797</v>
       </c>
       <c r="L10">
-        <v>199381356.229</v>
+        <v>199335627.972</v>
       </c>
       <c r="M10">
-        <v>180155169.799</v>
+        <v>180029617.927</v>
       </c>
       <c r="N10">
-        <v>219221866.499</v>
+        <v>219016398.963</v>
       </c>
     </row>
     <row r="11">
@@ -870,40 +870,40 @@
         </is>
       </c>
       <c r="C11">
-        <v>1655.942</v>
+        <v>1649.184</v>
       </c>
       <c r="D11">
-        <v>1495.513</v>
+        <v>1490.536</v>
       </c>
       <c r="E11">
-        <v>1826.721</v>
+        <v>1811.157</v>
       </c>
       <c r="F11">
-        <v>4130.312</v>
+        <v>4125.725</v>
       </c>
       <c r="G11">
-        <v>3731.665</v>
+        <v>3719.549</v>
       </c>
       <c r="H11">
-        <v>4544.685</v>
+        <v>4532.997</v>
       </c>
       <c r="I11">
-        <v>92278334.11</v>
+        <v>91858291.47</v>
       </c>
       <c r="J11">
-        <v>83297215.281</v>
+        <v>83034010.87199999</v>
       </c>
       <c r="K11">
-        <v>101236622.616</v>
+        <v>100873850.715</v>
       </c>
       <c r="L11">
-        <v>550948160.7309999</v>
+        <v>548534018.595</v>
       </c>
       <c r="M11">
-        <v>497261890.163</v>
+        <v>495115880.022</v>
       </c>
       <c r="N11">
-        <v>606035905.0930001</v>
+        <v>602662638.312</v>
       </c>
     </row>
     <row r="12">
@@ -918,40 +918,40 @@
         </is>
       </c>
       <c r="C12">
-        <v>3826.41</v>
+        <v>3817.15</v>
       </c>
       <c r="D12">
-        <v>3508.399</v>
+        <v>3491.984</v>
       </c>
       <c r="E12">
-        <v>4130.321</v>
+        <v>4145.918</v>
       </c>
       <c r="F12">
-        <v>6898.357</v>
+        <v>6897.372</v>
       </c>
       <c r="G12">
-        <v>6306.845</v>
+        <v>6317.389</v>
       </c>
       <c r="H12">
-        <v>7455.011</v>
+        <v>7492.105</v>
       </c>
       <c r="I12">
-        <v>213042006.713</v>
+        <v>212687676.656</v>
       </c>
       <c r="J12">
-        <v>194292600.203</v>
+        <v>194490774.826</v>
       </c>
       <c r="K12">
-        <v>230990153.552</v>
+        <v>230971771.558</v>
       </c>
       <c r="L12">
-        <v>918045721.977</v>
+        <v>917393404.156</v>
       </c>
       <c r="M12">
-        <v>839366792.12</v>
+        <v>840121068.671</v>
       </c>
       <c r="N12">
-        <v>994898771.734</v>
+        <v>995938655.985</v>
       </c>
     </row>
     <row r="13">
@@ -966,40 +966,40 @@
         </is>
       </c>
       <c r="C13">
-        <v>11563.843</v>
+        <v>11531.76</v>
       </c>
       <c r="D13">
-        <v>10616.131</v>
+        <v>10601.391</v>
       </c>
       <c r="E13">
-        <v>12481.841</v>
+        <v>12467.796</v>
       </c>
       <c r="F13">
-        <v>13729.715</v>
+        <v>13720.973</v>
       </c>
       <c r="G13">
-        <v>12643.455</v>
+        <v>12610.832</v>
       </c>
       <c r="H13">
-        <v>14867.5</v>
+        <v>14843.606</v>
       </c>
       <c r="I13">
-        <v>644276065.723</v>
+        <v>642507561.228</v>
       </c>
       <c r="J13">
-        <v>589658534.538</v>
+        <v>590890435.99</v>
       </c>
       <c r="K13">
-        <v>696036225.676</v>
+        <v>694586215.0470001</v>
       </c>
       <c r="L13">
-        <v>1829996179.632</v>
+        <v>1824948694.111</v>
       </c>
       <c r="M13">
-        <v>1681302803.057</v>
+        <v>1676995764.653</v>
       </c>
       <c r="N13">
-        <v>1981857352.689</v>
+        <v>1974370132.691</v>
       </c>
     </row>
     <row r="14">
@@ -1014,40 +1014,40 @@
         </is>
       </c>
       <c r="C14">
-        <v>13538.014</v>
+        <v>13479.389</v>
       </c>
       <c r="D14">
-        <v>12428.33</v>
+        <v>12350.822</v>
       </c>
       <c r="E14">
-        <v>14698.706</v>
+        <v>14612.432</v>
       </c>
       <c r="F14">
-        <v>8016.31</v>
+        <v>7979.999</v>
       </c>
       <c r="G14">
-        <v>7304.644</v>
+        <v>7274.532</v>
       </c>
       <c r="H14">
-        <v>8738.557000000001</v>
+        <v>8699.200000000001</v>
       </c>
       <c r="I14">
-        <v>755366163.563</v>
+        <v>750882864.795</v>
       </c>
       <c r="J14">
-        <v>693239971.174</v>
+        <v>688225614.717</v>
       </c>
       <c r="K14">
-        <v>817482948.803</v>
+        <v>813999464.178</v>
       </c>
       <c r="L14">
-        <v>1063107996.004</v>
+        <v>1061170243.357</v>
       </c>
       <c r="M14">
-        <v>963699824.914</v>
+        <v>966972667.477</v>
       </c>
       <c r="N14">
-        <v>1160748826.219</v>
+        <v>1156961687.294</v>
       </c>
     </row>
     <row r="15">
@@ -1062,40 +1062,40 @@
         </is>
       </c>
       <c r="C15">
-        <v>8914.869000000001</v>
+        <v>8916.040999999999</v>
       </c>
       <c r="D15">
-        <v>7806.172</v>
+        <v>7841.183</v>
       </c>
       <c r="E15">
-        <v>9966.436</v>
+        <v>10005.867</v>
       </c>
       <c r="F15">
-        <v>806.869</v>
+        <v>803.202</v>
       </c>
       <c r="G15">
-        <v>648.295</v>
+        <v>653.5890000000001</v>
       </c>
       <c r="H15">
-        <v>961.212</v>
+        <v>956.922</v>
       </c>
       <c r="I15">
-        <v>496291515.335</v>
+        <v>496700080.68</v>
       </c>
       <c r="J15">
-        <v>437562677.926</v>
+        <v>436975079.957</v>
       </c>
       <c r="K15">
-        <v>555988276.362</v>
+        <v>557326076.487</v>
       </c>
       <c r="L15">
-        <v>106518427.952</v>
+        <v>106806591.854</v>
       </c>
       <c r="M15">
-        <v>87311080.41</v>
+        <v>86909464.653</v>
       </c>
       <c r="N15">
-        <v>127234648.428</v>
+        <v>127239027.211</v>
       </c>
     </row>
     <row r="16">
@@ -1110,40 +1110,40 @@
         </is>
       </c>
       <c r="C16">
-        <v>1917.198</v>
+        <v>1952.845</v>
       </c>
       <c r="D16">
-        <v>1631.289</v>
+        <v>1649.096</v>
       </c>
       <c r="E16">
-        <v>2266.958</v>
+        <v>2297.25</v>
       </c>
       <c r="F16">
-        <v>6447.898</v>
+        <v>6580.855</v>
       </c>
       <c r="G16">
-        <v>5472.01</v>
+        <v>5529.373</v>
       </c>
       <c r="H16">
-        <v>7707.295</v>
+        <v>7766.892</v>
       </c>
       <c r="I16">
-        <v>28403747.681</v>
+        <v>28900668.814</v>
       </c>
       <c r="J16">
-        <v>24059333.791</v>
+        <v>24409402.948</v>
       </c>
       <c r="K16">
-        <v>33780360.935</v>
+        <v>33978283.335</v>
       </c>
       <c r="L16">
-        <v>858633947.796</v>
+        <v>875160992.608</v>
       </c>
       <c r="M16">
-        <v>722290493.344</v>
+        <v>736252721.0549999</v>
       </c>
       <c r="N16">
-        <v>1028333956.862</v>
+        <v>1034388505.602</v>
       </c>
     </row>
     <row r="17">
@@ -1158,40 +1158,40 @@
         </is>
       </c>
       <c r="C17">
-        <v>3265.399</v>
+        <v>3306.608</v>
       </c>
       <c r="D17">
-        <v>2769.57</v>
+        <v>2815.055</v>
       </c>
       <c r="E17">
-        <v>3808.305</v>
+        <v>3844.596</v>
       </c>
       <c r="F17">
-        <v>9240.889999999999</v>
+        <v>9350.343999999999</v>
       </c>
       <c r="G17">
-        <v>7917.718</v>
+        <v>7926.745</v>
       </c>
       <c r="H17">
-        <v>10924.55</v>
+        <v>10922.998</v>
       </c>
       <c r="I17">
-        <v>48273210.557</v>
+        <v>48969575.022</v>
       </c>
       <c r="J17">
-        <v>41734921.672</v>
+        <v>41693576.312</v>
       </c>
       <c r="K17">
-        <v>56250959.957</v>
+        <v>56948873.975</v>
       </c>
       <c r="L17">
-        <v>1226134489.862</v>
+        <v>1243844544.114</v>
       </c>
       <c r="M17">
-        <v>1045513110.285</v>
+        <v>1054663798.034</v>
       </c>
       <c r="N17">
-        <v>1441888853.297</v>
+        <v>1453351840.039</v>
       </c>
     </row>
     <row r="18">
@@ -1206,40 +1206,40 @@
         </is>
       </c>
       <c r="C18">
-        <v>4369.968</v>
+        <v>4361.168</v>
       </c>
       <c r="D18">
-        <v>3769.131</v>
+        <v>3768.369</v>
       </c>
       <c r="E18">
-        <v>4972.769</v>
+        <v>4999.142</v>
       </c>
       <c r="F18">
-        <v>9936.888000000001</v>
+        <v>9936.239</v>
       </c>
       <c r="G18">
-        <v>8551.02</v>
+        <v>8514.166999999999</v>
       </c>
       <c r="H18">
-        <v>11444.73</v>
+        <v>11480.48</v>
       </c>
       <c r="I18">
-        <v>64310906.607</v>
+        <v>64593974.665</v>
       </c>
       <c r="J18">
-        <v>55827523.771</v>
+        <v>55774451.088</v>
       </c>
       <c r="K18">
-        <v>73522532.083</v>
+        <v>74008623.699</v>
       </c>
       <c r="L18">
-        <v>1320617761.549</v>
+        <v>1321454092.399</v>
       </c>
       <c r="M18">
-        <v>1137454068.31</v>
+        <v>1132617701.065</v>
       </c>
       <c r="N18">
-        <v>1523865231.492</v>
+        <v>1525601934.695</v>
       </c>
     </row>
     <row r="19">
@@ -1254,40 +1254,40 @@
         </is>
       </c>
       <c r="C19">
-        <v>5639.376</v>
+        <v>5671.919</v>
       </c>
       <c r="D19">
-        <v>5004.504</v>
+        <v>5010.612</v>
       </c>
       <c r="E19">
-        <v>6371.068</v>
+        <v>6383.563</v>
       </c>
       <c r="F19">
-        <v>9243.893</v>
+        <v>9311.444</v>
       </c>
       <c r="G19">
-        <v>8161.669</v>
+        <v>8183.709</v>
       </c>
       <c r="H19">
-        <v>10425.105</v>
+        <v>10536.122</v>
       </c>
       <c r="I19">
-        <v>83540366.089</v>
+        <v>84023214.46699999</v>
       </c>
       <c r="J19">
-        <v>74111633.91500001</v>
+        <v>74254012.61399999</v>
       </c>
       <c r="K19">
-        <v>94080816.441</v>
+        <v>94490141.50399999</v>
       </c>
       <c r="L19">
-        <v>1223994388.003</v>
+        <v>1238123690.147</v>
       </c>
       <c r="M19">
-        <v>1083781314.988</v>
+        <v>1088455882.853</v>
       </c>
       <c r="N19">
-        <v>1392619026.69</v>
+        <v>1401743543.258</v>
       </c>
     </row>
     <row r="20">
@@ -1302,40 +1302,40 @@
         </is>
       </c>
       <c r="C20">
-        <v>8178.753</v>
+        <v>8266.556</v>
       </c>
       <c r="D20">
-        <v>7400.279</v>
+        <v>7448.184</v>
       </c>
       <c r="E20">
-        <v>9001.382</v>
+        <v>9120.189</v>
       </c>
       <c r="F20">
-        <v>8722.516</v>
+        <v>8796.642</v>
       </c>
       <c r="G20">
-        <v>7877.535</v>
+        <v>7898.353</v>
       </c>
       <c r="H20">
-        <v>9649.200000000001</v>
+        <v>9741.199000000001</v>
       </c>
       <c r="I20">
-        <v>121486018.913</v>
+        <v>122414435.631</v>
       </c>
       <c r="J20">
-        <v>109405496.248</v>
+        <v>110266268.454</v>
       </c>
       <c r="K20">
-        <v>134712140.95</v>
+        <v>135033040.226</v>
       </c>
       <c r="L20">
-        <v>1160715829.783</v>
+        <v>1170129284.558</v>
       </c>
       <c r="M20">
-        <v>1042061769.705</v>
+        <v>1050364756.171</v>
       </c>
       <c r="N20">
-        <v>1281670890.917</v>
+        <v>1295619464.775</v>
       </c>
     </row>
     <row r="21">
@@ -1350,40 +1350,40 @@
         </is>
       </c>
       <c r="C21">
-        <v>5433.317</v>
+        <v>5451.103</v>
       </c>
       <c r="D21">
-        <v>4826.162</v>
+        <v>4850.898</v>
       </c>
       <c r="E21">
-        <v>6106.711</v>
+        <v>6089.497</v>
       </c>
       <c r="F21">
-        <v>2766.454</v>
+        <v>2765.36</v>
       </c>
       <c r="G21">
-        <v>2453.571</v>
+        <v>2443.526</v>
       </c>
       <c r="H21">
-        <v>3118.312</v>
+        <v>3105.443</v>
       </c>
       <c r="I21">
-        <v>80502300</v>
+        <v>80714501.38500001</v>
       </c>
       <c r="J21">
-        <v>72031177.499</v>
+        <v>71806925.787</v>
       </c>
       <c r="K21">
-        <v>90016784.926</v>
+        <v>90119420.844</v>
       </c>
       <c r="L21">
-        <v>368195359.43</v>
+        <v>367568046.891</v>
       </c>
       <c r="M21">
-        <v>325941201.748</v>
+        <v>325117048.598</v>
       </c>
       <c r="N21">
-        <v>415630783.679</v>
+        <v>413142114.223</v>
       </c>
     </row>
     <row r="22">
@@ -1398,40 +1398,40 @@
         </is>
       </c>
       <c r="C22">
-        <v>2143.493</v>
+        <v>2158.21</v>
       </c>
       <c r="D22">
-        <v>1801.352</v>
+        <v>1795.918</v>
       </c>
       <c r="E22">
-        <v>2521.693</v>
+        <v>2554.605</v>
       </c>
       <c r="F22">
-        <v>146.07</v>
+        <v>145.259</v>
       </c>
       <c r="G22">
-        <v>113.221</v>
+        <v>112.009</v>
       </c>
       <c r="H22">
-        <v>180.378</v>
+        <v>181.373</v>
       </c>
       <c r="I22">
-        <v>31862946.4</v>
+        <v>31952567.92</v>
       </c>
       <c r="J22">
-        <v>26786898.415</v>
+        <v>26585100.083</v>
       </c>
       <c r="K22">
-        <v>36961267.335</v>
+        <v>37793151.379</v>
       </c>
       <c r="L22">
-        <v>19537637.437</v>
+        <v>19321888.827</v>
       </c>
       <c r="M22">
-        <v>15259988.454</v>
+        <v>14869176.547</v>
       </c>
       <c r="N22">
-        <v>24052411.339</v>
+        <v>24119334.695</v>
       </c>
     </row>
     <row r="23">
@@ -1446,40 +1446,40 @@
         </is>
       </c>
       <c r="C23">
-        <v>401.09</v>
+        <v>400.09</v>
       </c>
       <c r="D23">
-        <v>344.217</v>
+        <v>345.38</v>
       </c>
       <c r="E23">
-        <v>464.462</v>
+        <v>457.987</v>
       </c>
       <c r="F23">
-        <v>1610.817</v>
+        <v>1614.902</v>
       </c>
       <c r="G23">
-        <v>1395.601</v>
+        <v>1393.956</v>
       </c>
       <c r="H23">
-        <v>1875.905</v>
+        <v>1852.417</v>
       </c>
       <c r="I23">
-        <v>30233106.572</v>
+        <v>30071347.537</v>
       </c>
       <c r="J23">
-        <v>26114323.334</v>
+        <v>25999147.231</v>
       </c>
       <c r="K23">
-        <v>34716482.713</v>
+        <v>34464746.653</v>
       </c>
       <c r="L23">
-        <v>214610939.968</v>
+        <v>214781227.681</v>
       </c>
       <c r="M23">
-        <v>185408797.782</v>
+        <v>185396385.003</v>
       </c>
       <c r="N23">
-        <v>249986129.288</v>
+        <v>246541874.065</v>
       </c>
     </row>
     <row r="24">
@@ -1494,40 +1494,40 @@
         </is>
       </c>
       <c r="C24">
-        <v>647.039</v>
+        <v>650.548</v>
       </c>
       <c r="D24">
-        <v>568.308</v>
+        <v>567.0839999999999</v>
       </c>
       <c r="E24">
-        <v>732.651</v>
+        <v>738.454</v>
       </c>
       <c r="F24">
-        <v>2152.043</v>
+        <v>2166.54</v>
       </c>
       <c r="G24">
-        <v>1872.854</v>
+        <v>1887.222</v>
       </c>
       <c r="H24">
-        <v>2438.649</v>
+        <v>2462.845</v>
       </c>
       <c r="I24">
-        <v>48725641.982</v>
+        <v>48927754.262</v>
       </c>
       <c r="J24">
-        <v>42271394.502</v>
+        <v>42673218.437</v>
       </c>
       <c r="K24">
-        <v>54775070.397</v>
+        <v>55489801.656</v>
       </c>
       <c r="L24">
-        <v>287386460.221</v>
+        <v>288282283.139</v>
       </c>
       <c r="M24">
-        <v>250567773.441</v>
+        <v>251176085.306</v>
       </c>
       <c r="N24">
-        <v>325241667.42</v>
+        <v>327822220.957</v>
       </c>
     </row>
     <row r="25">
@@ -1542,40 +1542,40 @@
         </is>
       </c>
       <c r="C25">
-        <v>970.974</v>
+        <v>957.2619999999999</v>
       </c>
       <c r="D25">
-        <v>846.875</v>
+        <v>837.83</v>
       </c>
       <c r="E25">
-        <v>1104.651</v>
+        <v>1084.801</v>
       </c>
       <c r="F25">
-        <v>2556.926</v>
+        <v>2537.254</v>
       </c>
       <c r="G25">
-        <v>2221.837</v>
+        <v>2213.994</v>
       </c>
       <c r="H25">
-        <v>2904.348</v>
+        <v>2881.776</v>
       </c>
       <c r="I25">
-        <v>72690754.382</v>
+        <v>71996336.471</v>
       </c>
       <c r="J25">
-        <v>63324713.787</v>
+        <v>62979589.827</v>
       </c>
       <c r="K25">
-        <v>82689023.96600001</v>
+        <v>81563638.46799999</v>
       </c>
       <c r="L25">
-        <v>339899213.161</v>
+        <v>337523924.029</v>
       </c>
       <c r="M25">
-        <v>292764715.056</v>
+        <v>294366542.5</v>
       </c>
       <c r="N25">
-        <v>385273119.948</v>
+        <v>383713544.632</v>
       </c>
     </row>
     <row r="26">
@@ -1590,40 +1590,40 @@
         </is>
       </c>
       <c r="C26">
-        <v>1511.619</v>
+        <v>1513.701</v>
       </c>
       <c r="D26">
-        <v>1353.586</v>
+        <v>1348.935</v>
       </c>
       <c r="E26">
-        <v>1676.971</v>
+        <v>1685.009</v>
       </c>
       <c r="F26">
-        <v>2920.454</v>
+        <v>2928.898</v>
       </c>
       <c r="G26">
-        <v>2612.333</v>
+        <v>2611.03</v>
       </c>
       <c r="H26">
-        <v>3261.75</v>
+        <v>3266.41</v>
       </c>
       <c r="I26">
-        <v>113672615.55</v>
+        <v>113849019.309</v>
       </c>
       <c r="J26">
-        <v>101435683.768</v>
+        <v>101475674.885</v>
       </c>
       <c r="K26">
-        <v>126090126.629</v>
+        <v>126778072.472</v>
       </c>
       <c r="L26">
-        <v>388374755.532</v>
+        <v>389737779.953</v>
       </c>
       <c r="M26">
-        <v>346415902.113</v>
+        <v>347371486.411</v>
       </c>
       <c r="N26">
-        <v>433667668.386</v>
+        <v>434606953.573</v>
       </c>
     </row>
     <row r="27">
@@ -1638,40 +1638,40 @@
         </is>
       </c>
       <c r="C27">
-        <v>2146.853</v>
+        <v>2158.172</v>
       </c>
       <c r="D27">
-        <v>1925.766</v>
+        <v>1942.842</v>
       </c>
       <c r="E27">
-        <v>2368.481</v>
+        <v>2381.973</v>
       </c>
       <c r="F27">
-        <v>2774.407</v>
+        <v>2792.411</v>
       </c>
       <c r="G27">
-        <v>2495.435</v>
+        <v>2509.431</v>
       </c>
       <c r="H27">
-        <v>3058.849</v>
+        <v>3090.091</v>
       </c>
       <c r="I27">
-        <v>161244822.196</v>
+        <v>162272521.205</v>
       </c>
       <c r="J27">
-        <v>145133614.636</v>
+        <v>146146061.52</v>
       </c>
       <c r="K27">
-        <v>177532785.926</v>
+        <v>179010825.095</v>
       </c>
       <c r="L27">
-        <v>369355138.354</v>
+        <v>371585473.274</v>
       </c>
       <c r="M27">
-        <v>332860549.483</v>
+        <v>333913340.34</v>
       </c>
       <c r="N27">
-        <v>409132623.265</v>
+        <v>410636994.197</v>
       </c>
     </row>
     <row r="28">
@@ -1686,40 +1686,40 @@
         </is>
       </c>
       <c r="C28">
-        <v>695.645</v>
+        <v>691.979</v>
       </c>
       <c r="D28">
-        <v>615.9</v>
+        <v>617.2190000000001</v>
       </c>
       <c r="E28">
-        <v>773.514</v>
+        <v>769.889</v>
       </c>
       <c r="F28">
-        <v>457.737</v>
+        <v>456.84</v>
       </c>
       <c r="G28">
-        <v>405.597</v>
+        <v>402.609</v>
       </c>
       <c r="H28">
-        <v>517.944</v>
+        <v>513.433</v>
       </c>
       <c r="I28">
-        <v>52282584.442</v>
+        <v>52014218.343</v>
       </c>
       <c r="J28">
-        <v>46865484.186</v>
+        <v>46438277.531</v>
       </c>
       <c r="K28">
-        <v>57806005.417</v>
+        <v>57865197.03</v>
       </c>
       <c r="L28">
-        <v>60951467.44</v>
+        <v>60733912.41</v>
       </c>
       <c r="M28">
-        <v>53968816.058</v>
+        <v>53531639.805</v>
       </c>
       <c r="N28">
-        <v>68190681.016</v>
+        <v>68305380.12100001</v>
       </c>
     </row>
     <row r="29">
@@ -1734,40 +1734,40 @@
         </is>
       </c>
       <c r="C29">
-        <v>27.882</v>
+        <v>27.987</v>
       </c>
       <c r="D29">
-        <v>23.454</v>
+        <v>23.552</v>
       </c>
       <c r="E29">
-        <v>32.339</v>
+        <v>32.756</v>
       </c>
       <c r="F29">
-        <v>3.185</v>
+        <v>3.142</v>
       </c>
       <c r="G29">
-        <v>2.417</v>
+        <v>2.397</v>
       </c>
       <c r="H29">
-        <v>4.047</v>
+        <v>3.979</v>
       </c>
       <c r="I29">
-        <v>2100739.179</v>
+        <v>2103882.493</v>
       </c>
       <c r="J29">
-        <v>1771069.679</v>
+        <v>1770348.571</v>
       </c>
       <c r="K29">
-        <v>2434929.303</v>
+        <v>2460756.717</v>
       </c>
       <c r="L29">
-        <v>421254.282</v>
+        <v>418072.365</v>
       </c>
       <c r="M29">
-        <v>323352.966</v>
+        <v>318836.261</v>
       </c>
       <c r="N29">
-        <v>538199.227</v>
+        <v>529322.49</v>
       </c>
     </row>
     <row r="30">
@@ -1878,40 +1878,40 @@
         </is>
       </c>
       <c r="C32">
-        <v>162.679</v>
+        <v>162.64</v>
       </c>
       <c r="D32">
-        <v>147.779</v>
+        <v>147.163</v>
       </c>
       <c r="E32">
-        <v>178.217</v>
+        <v>178.509</v>
       </c>
       <c r="F32">
-        <v>1329.91</v>
+        <v>1324.574</v>
       </c>
       <c r="G32">
-        <v>1199.153</v>
+        <v>1193.992</v>
       </c>
       <c r="H32">
-        <v>1462.863</v>
+        <v>1458.277</v>
       </c>
       <c r="I32">
-        <v>2737167.064</v>
+        <v>2738838.345</v>
       </c>
       <c r="J32">
-        <v>2484778.139</v>
+        <v>2476963.059</v>
       </c>
       <c r="K32">
-        <v>3010145.539</v>
+        <v>3004999.044</v>
       </c>
       <c r="L32">
-        <v>176610315.952</v>
+        <v>176130220.716</v>
       </c>
       <c r="M32">
-        <v>158151951.514</v>
+        <v>158748435.972</v>
       </c>
       <c r="N32">
-        <v>194730361.24</v>
+        <v>194053867.538</v>
       </c>
     </row>
     <row r="33">
@@ -1926,40 +1926,40 @@
         </is>
       </c>
       <c r="C33">
-        <v>319.618</v>
+        <v>321.499</v>
       </c>
       <c r="D33">
-        <v>294.867</v>
+        <v>293.87</v>
       </c>
       <c r="E33">
-        <v>348.264</v>
+        <v>349.692</v>
       </c>
       <c r="F33">
-        <v>1905.454</v>
+        <v>1912.759</v>
       </c>
       <c r="G33">
-        <v>1739.272</v>
+        <v>1744.743</v>
       </c>
       <c r="H33">
-        <v>2069.518</v>
+        <v>2084.882</v>
       </c>
       <c r="I33">
-        <v>5379078.503</v>
+        <v>5414213.295</v>
       </c>
       <c r="J33">
-        <v>4945084.804</v>
+        <v>4949799.246</v>
       </c>
       <c r="K33">
-        <v>5838973.038</v>
+        <v>5886738.611</v>
       </c>
       <c r="L33">
-        <v>253409135.795</v>
+        <v>254374419.431</v>
       </c>
       <c r="M33">
-        <v>230714685.578</v>
+        <v>232044795.269</v>
       </c>
       <c r="N33">
-        <v>274986716.83</v>
+        <v>277283303.682</v>
       </c>
     </row>
     <row r="34">
@@ -1974,40 +1974,40 @@
         </is>
       </c>
       <c r="C34">
-        <v>1883.271</v>
+        <v>1880.944</v>
       </c>
       <c r="D34">
-        <v>1748.036</v>
+        <v>1741.727</v>
       </c>
       <c r="E34">
-        <v>2019.711</v>
+        <v>2022.463</v>
       </c>
       <c r="F34">
-        <v>7420.696</v>
+        <v>7428.571</v>
       </c>
       <c r="G34">
-        <v>6870.986</v>
+        <v>6852.84</v>
       </c>
       <c r="H34">
-        <v>8003.668</v>
+        <v>8006.327</v>
       </c>
       <c r="I34">
-        <v>31754949.478</v>
+        <v>31675589.924</v>
       </c>
       <c r="J34">
-        <v>29391480.793</v>
+        <v>29322580.703</v>
       </c>
       <c r="K34">
-        <v>33979423.539</v>
+        <v>34068213.539</v>
       </c>
       <c r="L34">
-        <v>988887885.061</v>
+        <v>987875281.286</v>
       </c>
       <c r="M34">
-        <v>912960822.768</v>
+        <v>911235268.645</v>
       </c>
       <c r="N34">
-        <v>1067806333.436</v>
+        <v>1065330516.456</v>
       </c>
     </row>
     <row r="35">
@@ -2022,40 +2022,40 @@
         </is>
       </c>
       <c r="C35">
-        <v>5154.379</v>
+        <v>5144.545</v>
       </c>
       <c r="D35">
-        <v>4734.898</v>
+        <v>4727.5</v>
       </c>
       <c r="E35">
-        <v>5598.342</v>
+        <v>5567.344</v>
       </c>
       <c r="F35">
-        <v>10459.062</v>
+        <v>10439.692</v>
       </c>
       <c r="G35">
-        <v>9491.358</v>
+        <v>9482.368</v>
       </c>
       <c r="H35">
-        <v>11436.462</v>
+        <v>11409.637</v>
       </c>
       <c r="I35">
-        <v>86732207.59100001</v>
+        <v>86646881.733</v>
       </c>
       <c r="J35">
-        <v>79795427.84900001</v>
+        <v>79659715.65700001</v>
       </c>
       <c r="K35">
-        <v>93783928.66599999</v>
+        <v>93754962.52599999</v>
       </c>
       <c r="L35">
-        <v>1387020056.841</v>
+        <v>1388583431.881</v>
       </c>
       <c r="M35">
-        <v>1263893915.627</v>
+        <v>1261388302.844</v>
       </c>
       <c r="N35">
-        <v>1515018851.788</v>
+        <v>1516629245.378</v>
       </c>
     </row>
     <row r="36">
@@ -2070,40 +2070,40 @@
         </is>
       </c>
       <c r="C36">
-        <v>6453.324</v>
+        <v>6421.702</v>
       </c>
       <c r="D36">
-        <v>5696.484</v>
+        <v>5678.141</v>
       </c>
       <c r="E36">
-        <v>7195.138</v>
+        <v>7179.698</v>
       </c>
       <c r="F36">
-        <v>2136.333</v>
+        <v>2131.272</v>
       </c>
       <c r="G36">
-        <v>1742.816</v>
+        <v>1739.501</v>
       </c>
       <c r="H36">
-        <v>2546.92</v>
+        <v>2530.787</v>
       </c>
       <c r="I36">
-        <v>108648331.767</v>
+        <v>108186844.145</v>
       </c>
       <c r="J36">
-        <v>95818084.147</v>
+        <v>95590398.45900001</v>
       </c>
       <c r="K36">
-        <v>121927659.742</v>
+        <v>120925815.132</v>
       </c>
       <c r="L36">
-        <v>283869363.35</v>
+        <v>283372929.325</v>
       </c>
       <c r="M36">
-        <v>230350724.62</v>
+        <v>231344660.877</v>
       </c>
       <c r="N36">
-        <v>337149907.29</v>
+        <v>336814247.731</v>
       </c>
     </row>
     <row r="37">
@@ -2118,22 +2118,22 @@
         </is>
       </c>
       <c r="C37">
-        <v>23559.005</v>
+        <v>23496.226</v>
       </c>
       <c r="D37">
-        <v>20901.512</v>
+        <v>20733.618</v>
       </c>
       <c r="E37">
-        <v>26428.759</v>
+        <v>26309.067</v>
       </c>
       <c r="F37">
-        <v>123312.546</v>
+        <v>2778.861</v>
       </c>
       <c r="G37">
-        <v>107850.827</v>
+        <v>2438.235</v>
       </c>
       <c r="H37">
-        <v>138877.449</v>
+        <v>3134.895</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -2145,13 +2145,13 @@
         <v>0</v>
       </c>
       <c r="L37">
-        <v>16396454786.054</v>
+        <v>369570793.574</v>
       </c>
       <c r="M37">
-        <v>14372137789.879</v>
+        <v>324407482.31</v>
       </c>
       <c r="N37">
-        <v>18553015929.35</v>
+        <v>416890272.485</v>
       </c>
     </row>
     <row r="38">
@@ -2166,22 +2166,22 @@
         </is>
       </c>
       <c r="C38">
-        <v>25295.549</v>
+        <v>25297.87</v>
       </c>
       <c r="D38">
-        <v>22516.642</v>
+        <v>22503.604</v>
       </c>
       <c r="E38">
-        <v>28077.784</v>
+        <v>28112.47</v>
       </c>
       <c r="F38">
-        <v>109392.771</v>
+        <v>2990.535</v>
       </c>
       <c r="G38">
-        <v>95811.265</v>
+        <v>2645.206</v>
       </c>
       <c r="H38">
-        <v>122953.886</v>
+        <v>3348.112</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2193,13 +2193,13 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>14542592931.754</v>
+        <v>397656058.842</v>
       </c>
       <c r="M38">
-        <v>12854321208.001</v>
+        <v>351720168.951</v>
       </c>
       <c r="N38">
-        <v>16275224508.697</v>
+        <v>444861351.913</v>
       </c>
     </row>
     <row r="39">
@@ -2214,22 +2214,22 @@
         </is>
       </c>
       <c r="C39">
-        <v>24013.514</v>
+        <v>24006.295</v>
       </c>
       <c r="D39">
-        <v>21509.144</v>
+        <v>21520.864</v>
       </c>
       <c r="E39">
-        <v>26471.427</v>
+        <v>26514.402</v>
       </c>
       <c r="F39">
-        <v>84290.71400000001</v>
+        <v>2838.83</v>
       </c>
       <c r="G39">
-        <v>74659.883</v>
+        <v>2531.542</v>
       </c>
       <c r="H39">
-        <v>93563.923</v>
+        <v>3156.225</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -2241,13 +2241,13 @@
         <v>0</v>
       </c>
       <c r="L39">
-        <v>11185964980.778</v>
+        <v>377638444.641</v>
       </c>
       <c r="M39">
-        <v>9874279752.856001</v>
+        <v>336775006.812</v>
       </c>
       <c r="N39">
-        <v>12511455998.05</v>
+        <v>419695850.26</v>
       </c>
     </row>
     <row r="40">
@@ -2262,22 +2262,22 @@
         </is>
       </c>
       <c r="C40">
-        <v>23434.585</v>
+        <v>23349.863</v>
       </c>
       <c r="D40">
-        <v>21162.861</v>
+        <v>21135.308</v>
       </c>
       <c r="E40">
-        <v>25651.16</v>
+        <v>25596.176</v>
       </c>
       <c r="F40">
-        <v>60092.374</v>
+        <v>2762.109</v>
       </c>
       <c r="G40">
-        <v>53855.583</v>
+        <v>2488.047</v>
       </c>
       <c r="H40">
-        <v>66692.90300000001</v>
+        <v>3042.927</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -2289,13 +2289,13 @@
         <v>0</v>
       </c>
       <c r="L40">
-        <v>7978345568.172</v>
+        <v>367339698.078</v>
       </c>
       <c r="M40">
-        <v>7166444698.575</v>
+        <v>331028451.795</v>
       </c>
       <c r="N40">
-        <v>8784602629.98</v>
+        <v>404802567.323</v>
       </c>
     </row>
     <row r="41">
@@ -2310,22 +2310,22 @@
         </is>
       </c>
       <c r="C41">
-        <v>28377.216</v>
+        <v>28405.421</v>
       </c>
       <c r="D41">
-        <v>26102.333</v>
+        <v>26112.666</v>
       </c>
       <c r="E41">
-        <v>30546.519</v>
+        <v>30707.416</v>
       </c>
       <c r="F41">
-        <v>49129.379</v>
+        <v>3360.027</v>
       </c>
       <c r="G41">
-        <v>44816.837</v>
+        <v>3075.819</v>
       </c>
       <c r="H41">
-        <v>53523.12</v>
+        <v>3649.886</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -2337,13 +2337,13 @@
         <v>0</v>
       </c>
       <c r="L41">
-        <v>6523212888.011</v>
+        <v>446808853.725</v>
       </c>
       <c r="M41">
-        <v>5942382308.346</v>
+        <v>409100824.487</v>
       </c>
       <c r="N41">
-        <v>7133433558.651</v>
+        <v>485261383.919</v>
       </c>
     </row>
     <row r="42">
@@ -2358,22 +2358,22 @@
         </is>
       </c>
       <c r="C42">
-        <v>19094.678</v>
+        <v>19086.567</v>
       </c>
       <c r="D42">
-        <v>17299.541</v>
+        <v>17358.172</v>
       </c>
       <c r="E42">
-        <v>20795.35</v>
+        <v>20829.429</v>
       </c>
       <c r="F42">
-        <v>17633.695</v>
+        <v>2249.555</v>
       </c>
       <c r="G42">
-        <v>15717.86</v>
+        <v>2036.459</v>
       </c>
       <c r="H42">
-        <v>19523.914</v>
+        <v>2468.638</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2385,13 +2385,13 @@
         <v>0</v>
       </c>
       <c r="L42">
-        <v>2347997551.758</v>
+        <v>299205409.541</v>
       </c>
       <c r="M42">
-        <v>2096361401.795</v>
+        <v>270982668.105</v>
       </c>
       <c r="N42">
-        <v>2612412243.326</v>
+        <v>328041214.407</v>
       </c>
     </row>
     <row r="43">
@@ -2406,22 +2406,22 @@
         </is>
       </c>
       <c r="C43">
-        <v>8257.860000000001</v>
+        <v>8263.718000000001</v>
       </c>
       <c r="D43">
-        <v>7242.891</v>
+        <v>7213.804</v>
       </c>
       <c r="E43">
-        <v>9296.152</v>
+        <v>9321.474</v>
       </c>
       <c r="F43">
-        <v>1337.694</v>
+        <v>524.409</v>
       </c>
       <c r="G43">
-        <v>1058.373</v>
+        <v>429.522</v>
       </c>
       <c r="H43">
-        <v>1602.884</v>
+        <v>623.777</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -2433,13 +2433,13 @@
         <v>0</v>
       </c>
       <c r="L43">
-        <v>178457499.929</v>
+        <v>69720704.037</v>
       </c>
       <c r="M43">
-        <v>141569586.384</v>
+        <v>57049396.848</v>
       </c>
       <c r="N43">
-        <v>214662293.659</v>
+        <v>82861488.765</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/Monte Carlo/HIA_per_age.xlsx
+++ b/output/Tables/2019/Monte Carlo/HIA_per_age.xlsx
@@ -438,22 +438,22 @@
         </is>
       </c>
       <c r="C2">
-        <v>448.754</v>
+        <v>448.881</v>
       </c>
       <c r="D2">
-        <v>403.952</v>
+        <v>404.061</v>
       </c>
       <c r="E2">
-        <v>493.54</v>
+        <v>493.764</v>
       </c>
       <c r="F2">
-        <v>25654.969</v>
+        <v>25661.048</v>
       </c>
       <c r="G2">
-        <v>23137.893</v>
+        <v>23149.48</v>
       </c>
       <c r="H2">
-        <v>28176.161</v>
+        <v>28188.391</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>3411965857.546</v>
+        <v>3413367908.633</v>
       </c>
       <c r="M2">
-        <v>3076430845.945</v>
+        <v>3077051548.6</v>
       </c>
       <c r="N2">
-        <v>3747683723.574</v>
+        <v>3749312382.159</v>
       </c>
     </row>
     <row r="3">
@@ -486,22 +486,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>862.462</v>
+        <v>862.102</v>
       </c>
       <c r="D3">
-        <v>785.526</v>
+        <v>785.114</v>
       </c>
       <c r="E3">
-        <v>939.177</v>
+        <v>938.76</v>
       </c>
       <c r="F3">
-        <v>40141.257</v>
+        <v>40127.176</v>
       </c>
       <c r="G3">
-        <v>36701.424</v>
+        <v>36682.29</v>
       </c>
       <c r="H3">
-        <v>43590.5</v>
+        <v>43567.89</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>5338426878.719</v>
+        <v>5335608852.862</v>
       </c>
       <c r="M3">
-        <v>4879561227.011</v>
+        <v>4877364553.002</v>
       </c>
       <c r="N3">
-        <v>5799989066.212</v>
+        <v>5797541661.361</v>
       </c>
     </row>
     <row r="4">
@@ -534,22 +534,22 @@
         </is>
       </c>
       <c r="C4">
-        <v>2288.788</v>
+        <v>2289.453</v>
       </c>
       <c r="D4">
-        <v>2095.715</v>
+        <v>2096.655</v>
       </c>
       <c r="E4">
-        <v>2480.551</v>
+        <v>2482.392</v>
       </c>
       <c r="F4">
-        <v>84961.026</v>
+        <v>84986.338</v>
       </c>
       <c r="G4">
-        <v>77960.683</v>
+        <v>77980.10799999999</v>
       </c>
       <c r="H4">
-        <v>91969.166</v>
+        <v>92004.262</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -561,13 +561,13 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>11303408325.729</v>
+        <v>11306582001.299</v>
       </c>
       <c r="M4">
-        <v>10369275160.191</v>
+        <v>10373718157.555</v>
       </c>
       <c r="N4">
-        <v>12242616587.612</v>
+        <v>12246881841.205</v>
       </c>
     </row>
     <row r="5">
@@ -582,22 +582,22 @@
         </is>
       </c>
       <c r="C5">
-        <v>4887.26</v>
+        <v>4888.182</v>
       </c>
       <c r="D5">
-        <v>4508.786</v>
+        <v>4509.408</v>
       </c>
       <c r="E5">
-        <v>5268.88</v>
+        <v>5268.584</v>
       </c>
       <c r="F5">
-        <v>131611.25</v>
+        <v>131630.18</v>
       </c>
       <c r="G5">
-        <v>121833.737</v>
+        <v>121868.876</v>
       </c>
       <c r="H5">
-        <v>141380.902</v>
+        <v>141394.04</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -609,13 +609,13 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>17505177919.406</v>
+        <v>17507786244.215</v>
       </c>
       <c r="M5">
-        <v>16201162240.009</v>
+        <v>16202173936.34</v>
       </c>
       <c r="N5">
-        <v>18810827198.624</v>
+        <v>18810623809.353</v>
       </c>
     </row>
     <row r="6">
@@ -630,22 +630,22 @@
         </is>
       </c>
       <c r="C6">
-        <v>10426.459</v>
+        <v>10426.88</v>
       </c>
       <c r="D6">
-        <v>9654.338</v>
+        <v>9655.201999999999</v>
       </c>
       <c r="E6">
-        <v>11200.527</v>
+        <v>11199.853</v>
       </c>
       <c r="F6">
-        <v>178163.438</v>
+        <v>178176.338</v>
       </c>
       <c r="G6">
-        <v>165584.761</v>
+        <v>165600.046</v>
       </c>
       <c r="H6">
-        <v>190787.25</v>
+        <v>190792.755</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -657,13 +657,13 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>23696310362.035</v>
+        <v>23697957726.828</v>
       </c>
       <c r="M6">
-        <v>22021518575.122</v>
+        <v>22021214703.766</v>
       </c>
       <c r="N6">
-        <v>25372420292.966</v>
+        <v>25374444613.86</v>
       </c>
     </row>
     <row r="7">
@@ -678,22 +678,22 @@
         </is>
       </c>
       <c r="C7">
-        <v>16760.506</v>
+        <v>16762.317</v>
       </c>
       <c r="D7">
-        <v>15370.659</v>
+        <v>15372.847</v>
       </c>
       <c r="E7">
-        <v>18151.309</v>
+        <v>18151.877</v>
       </c>
       <c r="F7">
-        <v>124288.34</v>
+        <v>124304.27</v>
       </c>
       <c r="G7">
-        <v>115237.817</v>
+        <v>115267.277</v>
       </c>
       <c r="H7">
-        <v>133327.512</v>
+        <v>133335.387</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>16527494927.454</v>
+        <v>16528458707.039</v>
       </c>
       <c r="M7">
-        <v>15333039407.126</v>
+        <v>15334222716.125</v>
       </c>
       <c r="N7">
-        <v>17727583611.788</v>
+        <v>17728714613.48</v>
       </c>
     </row>
     <row r="8">
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="C8">
-        <v>22820.376</v>
+        <v>22822.878</v>
       </c>
       <c r="D8">
-        <v>20283.101</v>
+        <v>20290.443</v>
       </c>
       <c r="E8">
-        <v>25359.155</v>
+        <v>25355.627</v>
       </c>
       <c r="F8">
-        <v>19968.089</v>
+        <v>19973.951</v>
       </c>
       <c r="G8">
-        <v>16870.066</v>
+        <v>16877.026</v>
       </c>
       <c r="H8">
-        <v>23074.378</v>
+        <v>23083.128</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -753,13 +753,13 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>2655058613.693</v>
+        <v>2656295622.175</v>
       </c>
       <c r="M8">
-        <v>2243773621.972</v>
+        <v>2244317322.153</v>
       </c>
       <c r="N8">
-        <v>3068130030.275</v>
+        <v>3069614965.075</v>
       </c>
     </row>
     <row r="9">
@@ -774,40 +774,40 @@
         </is>
       </c>
       <c r="C9">
-        <v>230.179</v>
+        <v>231.468</v>
       </c>
       <c r="D9">
-        <v>205.23</v>
+        <v>206.419</v>
       </c>
       <c r="E9">
-        <v>255.416</v>
+        <v>256.89</v>
       </c>
       <c r="F9">
-        <v>872.289</v>
+        <v>877.592</v>
       </c>
       <c r="G9">
-        <v>778.341</v>
+        <v>782.499</v>
       </c>
       <c r="H9">
-        <v>968.919</v>
+        <v>974.639</v>
       </c>
       <c r="I9">
-        <v>12818083.091</v>
+        <v>12890666.187</v>
       </c>
       <c r="J9">
-        <v>11436698.683</v>
+        <v>11501468.723</v>
       </c>
       <c r="K9">
-        <v>14222118.27</v>
+        <v>14299854.51</v>
       </c>
       <c r="L9">
-        <v>116007810.948</v>
+        <v>116703537.322</v>
       </c>
       <c r="M9">
-        <v>103478035.473</v>
+        <v>104060253.596</v>
       </c>
       <c r="N9">
-        <v>128826546.903</v>
+        <v>129575165.257</v>
       </c>
     </row>
     <row r="10">
@@ -822,40 +822,40 @@
         </is>
       </c>
       <c r="C10">
-        <v>479.633</v>
+        <v>481.282</v>
       </c>
       <c r="D10">
-        <v>433.222</v>
+        <v>434.393</v>
       </c>
       <c r="E10">
-        <v>526.566</v>
+        <v>528.215</v>
       </c>
       <c r="F10">
-        <v>1499.014</v>
+        <v>1503.523</v>
       </c>
       <c r="G10">
-        <v>1354.43</v>
+        <v>1358.291</v>
       </c>
       <c r="H10">
-        <v>1646.415</v>
+        <v>1650.94</v>
       </c>
       <c r="I10">
-        <v>26710382.684</v>
+        <v>26799865.883</v>
       </c>
       <c r="J10">
-        <v>24124674.183</v>
+        <v>24212829.351</v>
       </c>
       <c r="K10">
-        <v>29348738.797</v>
+        <v>29452200.133</v>
       </c>
       <c r="L10">
-        <v>199335627.972</v>
+        <v>199996469.873</v>
       </c>
       <c r="M10">
-        <v>180029617.927</v>
+        <v>180571637.229</v>
       </c>
       <c r="N10">
-        <v>219016398.963</v>
+        <v>219691217.67</v>
       </c>
     </row>
     <row r="11">
@@ -870,40 +870,40 @@
         </is>
       </c>
       <c r="C11">
-        <v>1649.184</v>
+        <v>1647.861</v>
       </c>
       <c r="D11">
-        <v>1490.536</v>
+        <v>1488.811</v>
       </c>
       <c r="E11">
-        <v>1811.157</v>
+        <v>1810.014</v>
       </c>
       <c r="F11">
-        <v>4125.725</v>
+        <v>4121.355</v>
       </c>
       <c r="G11">
-        <v>3719.549</v>
+        <v>3715.11</v>
       </c>
       <c r="H11">
-        <v>4532.997</v>
+        <v>4531.834</v>
       </c>
       <c r="I11">
-        <v>91858291.47</v>
+        <v>91772135.52500001</v>
       </c>
       <c r="J11">
-        <v>83034010.87199999</v>
+        <v>82935928.38</v>
       </c>
       <c r="K11">
-        <v>100873850.715</v>
+        <v>100826803.598</v>
       </c>
       <c r="L11">
-        <v>548534018.595</v>
+        <v>548010254.709</v>
       </c>
       <c r="M11">
-        <v>495115880.022</v>
+        <v>494578325.582</v>
       </c>
       <c r="N11">
-        <v>602662638.312</v>
+        <v>602509122.135</v>
       </c>
     </row>
     <row r="12">
@@ -918,40 +918,40 @@
         </is>
       </c>
       <c r="C12">
-        <v>3817.15</v>
+        <v>3823.528</v>
       </c>
       <c r="D12">
-        <v>3491.984</v>
+        <v>3496.993</v>
       </c>
       <c r="E12">
-        <v>4145.918</v>
+        <v>4154.72</v>
       </c>
       <c r="F12">
-        <v>6897.372</v>
+        <v>6909.359</v>
       </c>
       <c r="G12">
-        <v>6317.389</v>
+        <v>6329.93</v>
       </c>
       <c r="H12">
-        <v>7492.105</v>
+        <v>7505.347</v>
       </c>
       <c r="I12">
-        <v>212687676.656</v>
+        <v>213026796.361</v>
       </c>
       <c r="J12">
-        <v>194490774.826</v>
+        <v>194762852.487</v>
       </c>
       <c r="K12">
-        <v>230971771.558</v>
+        <v>231438092.679</v>
       </c>
       <c r="L12">
-        <v>917393404.156</v>
+        <v>919113332.76</v>
       </c>
       <c r="M12">
-        <v>840121068.671</v>
+        <v>841018384.376</v>
       </c>
       <c r="N12">
-        <v>995938655.985</v>
+        <v>997977767.778</v>
       </c>
     </row>
     <row r="13">
@@ -966,40 +966,40 @@
         </is>
       </c>
       <c r="C13">
-        <v>11531.76</v>
+        <v>11570.135</v>
       </c>
       <c r="D13">
-        <v>10601.391</v>
+        <v>10637.371</v>
       </c>
       <c r="E13">
-        <v>12467.796</v>
+        <v>12509.299</v>
       </c>
       <c r="F13">
-        <v>13720.973</v>
+        <v>13759.138</v>
       </c>
       <c r="G13">
-        <v>12610.832</v>
+        <v>12643.543</v>
       </c>
       <c r="H13">
-        <v>14843.606</v>
+        <v>14888.457</v>
       </c>
       <c r="I13">
-        <v>642507561.228</v>
+        <v>644602554.651</v>
       </c>
       <c r="J13">
-        <v>590890435.99</v>
+        <v>592660439.841</v>
       </c>
       <c r="K13">
-        <v>694586215.0470001</v>
+        <v>697214535.448</v>
       </c>
       <c r="L13">
-        <v>1824948694.111</v>
+        <v>1829634863.588</v>
       </c>
       <c r="M13">
-        <v>1676995764.653</v>
+        <v>1682011926.122</v>
       </c>
       <c r="N13">
-        <v>1974370132.691</v>
+        <v>1980176564.87</v>
       </c>
     </row>
     <row r="14">
@@ -1014,40 +1014,40 @@
         </is>
       </c>
       <c r="C14">
-        <v>13479.389</v>
+        <v>13474.561</v>
       </c>
       <c r="D14">
-        <v>12350.822</v>
+        <v>12346.089</v>
       </c>
       <c r="E14">
-        <v>14612.432</v>
+        <v>14610.713</v>
       </c>
       <c r="F14">
-        <v>7979.999</v>
+        <v>7965.662</v>
       </c>
       <c r="G14">
-        <v>7274.532</v>
+        <v>7263.037</v>
       </c>
       <c r="H14">
-        <v>8699.200000000001</v>
+        <v>8681.614</v>
       </c>
       <c r="I14">
-        <v>750882864.795</v>
+        <v>750587534.855</v>
       </c>
       <c r="J14">
-        <v>688225614.717</v>
+        <v>687778953.349</v>
       </c>
       <c r="K14">
-        <v>813999464.178</v>
+        <v>813823506.0930001</v>
       </c>
       <c r="L14">
-        <v>1061170243.357</v>
+        <v>1059232396.389</v>
       </c>
       <c r="M14">
-        <v>966972667.477</v>
+        <v>965601478.153</v>
       </c>
       <c r="N14">
-        <v>1156961687.294</v>
+        <v>1154179083.47</v>
       </c>
     </row>
     <row r="15">
@@ -1062,40 +1062,40 @@
         </is>
       </c>
       <c r="C15">
-        <v>8916.040999999999</v>
+        <v>8918.674000000001</v>
       </c>
       <c r="D15">
-        <v>7841.183</v>
+        <v>7839.139</v>
       </c>
       <c r="E15">
-        <v>10005.867</v>
+        <v>10010.111</v>
       </c>
       <c r="F15">
-        <v>803.202</v>
+        <v>800.1319999999999</v>
       </c>
       <c r="G15">
-        <v>653.5890000000001</v>
+        <v>650.793</v>
       </c>
       <c r="H15">
-        <v>956.922</v>
+        <v>953.356</v>
       </c>
       <c r="I15">
-        <v>496700080.68</v>
+        <v>496823901.628</v>
       </c>
       <c r="J15">
-        <v>436975079.957</v>
+        <v>436920031.444</v>
       </c>
       <c r="K15">
-        <v>557326076.487</v>
+        <v>557763925.545</v>
       </c>
       <c r="L15">
-        <v>106806591.854</v>
+        <v>106364010.698</v>
       </c>
       <c r="M15">
-        <v>86909464.653</v>
+        <v>86567217.977</v>
       </c>
       <c r="N15">
-        <v>127239027.211</v>
+        <v>126741866.495</v>
       </c>
     </row>
     <row r="16">
@@ -1110,40 +1110,40 @@
         </is>
       </c>
       <c r="C16">
-        <v>1952.845</v>
+        <v>1951.787</v>
       </c>
       <c r="D16">
-        <v>1649.096</v>
+        <v>1644.918</v>
       </c>
       <c r="E16">
-        <v>2297.25</v>
+        <v>2296.406</v>
       </c>
       <c r="F16">
-        <v>6580.855</v>
+        <v>6580.584</v>
       </c>
       <c r="G16">
-        <v>5529.373</v>
+        <v>5519.485</v>
       </c>
       <c r="H16">
-        <v>7766.892</v>
+        <v>7779.228</v>
       </c>
       <c r="I16">
-        <v>28900668.814</v>
+        <v>28890813.119</v>
       </c>
       <c r="J16">
-        <v>24409402.948</v>
+        <v>24343265.966</v>
       </c>
       <c r="K16">
-        <v>33978283.335</v>
+        <v>33976567.704</v>
       </c>
       <c r="L16">
-        <v>875160992.608</v>
+        <v>874994707.209</v>
       </c>
       <c r="M16">
-        <v>736252721.0549999</v>
+        <v>734430247.4349999</v>
       </c>
       <c r="N16">
-        <v>1034388505.602</v>
+        <v>1035094423.077</v>
       </c>
     </row>
     <row r="17">
@@ -1158,40 +1158,40 @@
         </is>
       </c>
       <c r="C17">
-        <v>3306.608</v>
+        <v>3338.79</v>
       </c>
       <c r="D17">
-        <v>2815.055</v>
+        <v>2843.541</v>
       </c>
       <c r="E17">
-        <v>3844.596</v>
+        <v>3881.182</v>
       </c>
       <c r="F17">
-        <v>9350.343999999999</v>
+        <v>9446.579</v>
       </c>
       <c r="G17">
-        <v>7926.745</v>
+        <v>8008.247</v>
       </c>
       <c r="H17">
-        <v>10922.998</v>
+        <v>11044.203</v>
       </c>
       <c r="I17">
-        <v>48969575.022</v>
+        <v>49442844.14</v>
       </c>
       <c r="J17">
-        <v>41693576.312</v>
+        <v>42088662.021</v>
       </c>
       <c r="K17">
-        <v>56948873.975</v>
+        <v>57576181.708</v>
       </c>
       <c r="L17">
-        <v>1243844544.114</v>
+        <v>1256908493.784</v>
       </c>
       <c r="M17">
-        <v>1054663798.034</v>
+        <v>1065125609.667</v>
       </c>
       <c r="N17">
-        <v>1453351840.039</v>
+        <v>1468824204.678</v>
       </c>
     </row>
     <row r="18">
@@ -1206,40 +1206,40 @@
         </is>
       </c>
       <c r="C18">
-        <v>4361.168</v>
+        <v>4368.521</v>
       </c>
       <c r="D18">
-        <v>3768.369</v>
+        <v>3782.189</v>
       </c>
       <c r="E18">
-        <v>4999.142</v>
+        <v>5017.386</v>
       </c>
       <c r="F18">
-        <v>9936.239</v>
+        <v>9949.815000000001</v>
       </c>
       <c r="G18">
-        <v>8514.166999999999</v>
+        <v>8539.005999999999</v>
       </c>
       <c r="H18">
-        <v>11480.48</v>
+        <v>11517.252</v>
       </c>
       <c r="I18">
-        <v>64593974.665</v>
+        <v>64713820.485</v>
       </c>
       <c r="J18">
-        <v>55774451.088</v>
+        <v>55914716.23</v>
       </c>
       <c r="K18">
-        <v>74008623.699</v>
+        <v>74287071.97</v>
       </c>
       <c r="L18">
-        <v>1321454092.399</v>
+        <v>1323287545.276</v>
       </c>
       <c r="M18">
-        <v>1132617701.065</v>
+        <v>1135273739.334</v>
       </c>
       <c r="N18">
-        <v>1525601934.695</v>
+        <v>1529842983.382</v>
       </c>
     </row>
     <row r="19">
@@ -1254,40 +1254,40 @@
         </is>
       </c>
       <c r="C19">
-        <v>5671.919</v>
+        <v>5686.614</v>
       </c>
       <c r="D19">
-        <v>5010.612</v>
+        <v>5026.382</v>
       </c>
       <c r="E19">
-        <v>6383.563</v>
+        <v>6393.554</v>
       </c>
       <c r="F19">
-        <v>9311.444</v>
+        <v>9333.874</v>
       </c>
       <c r="G19">
-        <v>8183.709</v>
+        <v>8208.231</v>
       </c>
       <c r="H19">
-        <v>10536.122</v>
+        <v>10554.205</v>
       </c>
       <c r="I19">
-        <v>84023214.46699999</v>
+        <v>84237443.898</v>
       </c>
       <c r="J19">
-        <v>74254012.61399999</v>
+        <v>74485210.248</v>
       </c>
       <c r="K19">
-        <v>94490141.50399999</v>
+        <v>94681258.079</v>
       </c>
       <c r="L19">
-        <v>1238123690.147</v>
+        <v>1241098891.948</v>
       </c>
       <c r="M19">
-        <v>1088455882.853</v>
+        <v>1091427702.345</v>
       </c>
       <c r="N19">
-        <v>1401743543.258</v>
+        <v>1403245528.501</v>
       </c>
     </row>
     <row r="20">
@@ -1302,40 +1302,40 @@
         </is>
       </c>
       <c r="C20">
-        <v>8266.556</v>
+        <v>8235.025</v>
       </c>
       <c r="D20">
-        <v>7448.184</v>
+        <v>7411.591</v>
       </c>
       <c r="E20">
-        <v>9120.189</v>
+        <v>9092.906000000001</v>
       </c>
       <c r="F20">
-        <v>8796.642</v>
+        <v>8761.965</v>
       </c>
       <c r="G20">
-        <v>7898.353</v>
+        <v>7862.49</v>
       </c>
       <c r="H20">
-        <v>9741.199000000001</v>
+        <v>9709.539000000001</v>
       </c>
       <c r="I20">
-        <v>122414435.631</v>
+        <v>121920897.405</v>
       </c>
       <c r="J20">
-        <v>110266268.454</v>
+        <v>109754555.155</v>
       </c>
       <c r="K20">
-        <v>135033040.226</v>
+        <v>134707210.923</v>
       </c>
       <c r="L20">
-        <v>1170129284.558</v>
+        <v>1165241977.011</v>
       </c>
       <c r="M20">
-        <v>1050364756.171</v>
+        <v>1045149169.389</v>
       </c>
       <c r="N20">
-        <v>1295619464.775</v>
+        <v>1290602568.016</v>
       </c>
     </row>
     <row r="21">
@@ -1350,40 +1350,40 @@
         </is>
       </c>
       <c r="C21">
-        <v>5451.103</v>
+        <v>5437.258</v>
       </c>
       <c r="D21">
-        <v>4850.898</v>
+        <v>4838.559</v>
       </c>
       <c r="E21">
-        <v>6089.497</v>
+        <v>6081.163</v>
       </c>
       <c r="F21">
-        <v>2765.36</v>
+        <v>2757.669</v>
       </c>
       <c r="G21">
-        <v>2443.526</v>
+        <v>2436.882</v>
       </c>
       <c r="H21">
-        <v>3105.443</v>
+        <v>3099.235</v>
       </c>
       <c r="I21">
-        <v>80714501.38500001</v>
+        <v>80518514.348</v>
       </c>
       <c r="J21">
-        <v>71806925.787</v>
+        <v>71634192.397</v>
       </c>
       <c r="K21">
-        <v>90119420.844</v>
+        <v>89921844.226</v>
       </c>
       <c r="L21">
-        <v>367568046.891</v>
+        <v>366575200.061</v>
       </c>
       <c r="M21">
-        <v>325117048.598</v>
+        <v>323853617.622</v>
       </c>
       <c r="N21">
-        <v>413142114.223</v>
+        <v>412327969.112</v>
       </c>
     </row>
     <row r="22">
@@ -1398,40 +1398,40 @@
         </is>
       </c>
       <c r="C22">
-        <v>2158.21</v>
+        <v>2155.382</v>
       </c>
       <c r="D22">
-        <v>1795.918</v>
+        <v>1794.829</v>
       </c>
       <c r="E22">
-        <v>2554.605</v>
+        <v>2555.166</v>
       </c>
       <c r="F22">
-        <v>145.259</v>
+        <v>144.243</v>
       </c>
       <c r="G22">
-        <v>112.009</v>
+        <v>111.566</v>
       </c>
       <c r="H22">
-        <v>181.373</v>
+        <v>180.772</v>
       </c>
       <c r="I22">
-        <v>31952567.92</v>
+        <v>31906548.178</v>
       </c>
       <c r="J22">
-        <v>26585100.083</v>
+        <v>26558703.613</v>
       </c>
       <c r="K22">
-        <v>37793151.379</v>
+        <v>37794850.719</v>
       </c>
       <c r="L22">
-        <v>19321888.827</v>
+        <v>19186967.579</v>
       </c>
       <c r="M22">
-        <v>14869176.547</v>
+        <v>14810810.884</v>
       </c>
       <c r="N22">
-        <v>24119334.695</v>
+        <v>24006366.264</v>
       </c>
     </row>
     <row r="23">
@@ -1446,40 +1446,40 @@
         </is>
       </c>
       <c r="C23">
-        <v>400.09</v>
+        <v>402.184</v>
       </c>
       <c r="D23">
-        <v>345.38</v>
+        <v>347.535</v>
       </c>
       <c r="E23">
-        <v>457.987</v>
+        <v>460.616</v>
       </c>
       <c r="F23">
-        <v>1614.902</v>
+        <v>1623.363</v>
       </c>
       <c r="G23">
-        <v>1393.956</v>
+        <v>1400.442</v>
       </c>
       <c r="H23">
-        <v>1852.417</v>
+        <v>1860.364</v>
       </c>
       <c r="I23">
-        <v>30071347.537</v>
+        <v>30243919.246</v>
       </c>
       <c r="J23">
-        <v>25999147.231</v>
+        <v>26149030.608</v>
       </c>
       <c r="K23">
-        <v>34464746.653</v>
+        <v>34612589.968</v>
       </c>
       <c r="L23">
-        <v>214781227.681</v>
+        <v>215887823.619</v>
       </c>
       <c r="M23">
-        <v>185396385.003</v>
+        <v>186323826.539</v>
       </c>
       <c r="N23">
-        <v>246541874.065</v>
+        <v>247712166.668</v>
       </c>
     </row>
     <row r="24">
@@ -1494,40 +1494,40 @@
         </is>
       </c>
       <c r="C24">
-        <v>650.548</v>
+        <v>644.348</v>
       </c>
       <c r="D24">
-        <v>567.0839999999999</v>
+        <v>561.598</v>
       </c>
       <c r="E24">
-        <v>738.454</v>
+        <v>732.129</v>
       </c>
       <c r="F24">
-        <v>2166.54</v>
+        <v>2143.82</v>
       </c>
       <c r="G24">
-        <v>1887.222</v>
+        <v>1868.474</v>
       </c>
       <c r="H24">
-        <v>2462.845</v>
+        <v>2439.804</v>
       </c>
       <c r="I24">
-        <v>48927754.262</v>
+        <v>48456988.146</v>
       </c>
       <c r="J24">
-        <v>42673218.437</v>
+        <v>42276049.557</v>
       </c>
       <c r="K24">
-        <v>55489801.656</v>
+        <v>55028968.612</v>
       </c>
       <c r="L24">
-        <v>288282283.139</v>
+        <v>285249093.143</v>
       </c>
       <c r="M24">
-        <v>251176085.306</v>
+        <v>248511303.194</v>
       </c>
       <c r="N24">
-        <v>327822220.957</v>
+        <v>324700607.839</v>
       </c>
     </row>
     <row r="25">
@@ -1542,40 +1542,40 @@
         </is>
       </c>
       <c r="C25">
-        <v>957.2619999999999</v>
+        <v>955.9400000000001</v>
       </c>
       <c r="D25">
-        <v>837.83</v>
+        <v>836.7380000000001</v>
       </c>
       <c r="E25">
-        <v>1084.801</v>
+        <v>1083.004</v>
       </c>
       <c r="F25">
-        <v>2537.254</v>
+        <v>2533.535</v>
       </c>
       <c r="G25">
-        <v>2213.994</v>
+        <v>2211.945</v>
       </c>
       <c r="H25">
-        <v>2881.776</v>
+        <v>2877.382</v>
       </c>
       <c r="I25">
-        <v>71996336.471</v>
+        <v>71896542.059</v>
       </c>
       <c r="J25">
-        <v>62979589.827</v>
+        <v>62933450.119</v>
       </c>
       <c r="K25">
-        <v>81563638.46799999</v>
+        <v>81482599.82099999</v>
       </c>
       <c r="L25">
-        <v>337523924.029</v>
+        <v>336966107.378</v>
       </c>
       <c r="M25">
-        <v>294366542.5</v>
+        <v>294198806.52</v>
       </c>
       <c r="N25">
-        <v>383713544.632</v>
+        <v>382612798.696</v>
       </c>
     </row>
     <row r="26">
@@ -1590,40 +1590,40 @@
         </is>
       </c>
       <c r="C26">
-        <v>1513.701</v>
+        <v>1514.418</v>
       </c>
       <c r="D26">
-        <v>1348.935</v>
+        <v>1350.086</v>
       </c>
       <c r="E26">
-        <v>1685.009</v>
+        <v>1688.644</v>
       </c>
       <c r="F26">
-        <v>2928.898</v>
+        <v>2930.577</v>
       </c>
       <c r="G26">
-        <v>2611.03</v>
+        <v>2610.459</v>
       </c>
       <c r="H26">
-        <v>3266.41</v>
+        <v>3270.774</v>
       </c>
       <c r="I26">
-        <v>113849019.309</v>
+        <v>113905266.055</v>
       </c>
       <c r="J26">
-        <v>101475674.885</v>
+        <v>101483549.667</v>
       </c>
       <c r="K26">
-        <v>126778072.472</v>
+        <v>126984830.849</v>
       </c>
       <c r="L26">
-        <v>389737779.953</v>
+        <v>389951026.195</v>
       </c>
       <c r="M26">
-        <v>347371486.411</v>
+        <v>347210737.359</v>
       </c>
       <c r="N26">
-        <v>434606953.573</v>
+        <v>435020809.582</v>
       </c>
     </row>
     <row r="27">
@@ -1638,40 +1638,40 @@
         </is>
       </c>
       <c r="C27">
-        <v>2158.172</v>
+        <v>2162.381</v>
       </c>
       <c r="D27">
-        <v>1942.842</v>
+        <v>1947.109</v>
       </c>
       <c r="E27">
-        <v>2381.973</v>
+        <v>2387.461</v>
       </c>
       <c r="F27">
-        <v>2792.411</v>
+        <v>2801.379</v>
       </c>
       <c r="G27">
-        <v>2509.431</v>
+        <v>2516.722</v>
       </c>
       <c r="H27">
-        <v>3090.091</v>
+        <v>3098.76</v>
       </c>
       <c r="I27">
-        <v>162272521.205</v>
+        <v>162613031.518</v>
       </c>
       <c r="J27">
-        <v>146146061.52</v>
+        <v>146368806.884</v>
       </c>
       <c r="K27">
-        <v>179010825.095</v>
+        <v>179413619.18</v>
       </c>
       <c r="L27">
-        <v>371585473.274</v>
+        <v>372727955.56</v>
       </c>
       <c r="M27">
-        <v>333913340.34</v>
+        <v>334856770.064</v>
       </c>
       <c r="N27">
-        <v>410636994.197</v>
+        <v>412288546.64</v>
       </c>
     </row>
     <row r="28">
@@ -1686,40 +1686,40 @@
         </is>
       </c>
       <c r="C28">
-        <v>691.979</v>
+        <v>696.09</v>
       </c>
       <c r="D28">
-        <v>617.2190000000001</v>
+        <v>620.8579999999999</v>
       </c>
       <c r="E28">
-        <v>769.889</v>
+        <v>775.0940000000001</v>
       </c>
       <c r="F28">
-        <v>456.84</v>
+        <v>460.08</v>
       </c>
       <c r="G28">
-        <v>402.609</v>
+        <v>405.411</v>
       </c>
       <c r="H28">
-        <v>513.433</v>
+        <v>518.1369999999999</v>
       </c>
       <c r="I28">
-        <v>52014218.343</v>
+        <v>52337664.788</v>
       </c>
       <c r="J28">
-        <v>46438277.531</v>
+        <v>46698636.272</v>
       </c>
       <c r="K28">
-        <v>57865197.03</v>
+        <v>58255435.575</v>
       </c>
       <c r="L28">
-        <v>60733912.41</v>
+        <v>61183221.944</v>
       </c>
       <c r="M28">
-        <v>53531639.805</v>
+        <v>53905108.468</v>
       </c>
       <c r="N28">
-        <v>68305380.12100001</v>
+        <v>68891012.13</v>
       </c>
     </row>
     <row r="29">
@@ -1734,40 +1734,40 @@
         </is>
       </c>
       <c r="C29">
-        <v>27.987</v>
+        <v>27.72</v>
       </c>
       <c r="D29">
-        <v>23.552</v>
+        <v>23.339</v>
       </c>
       <c r="E29">
-        <v>32.756</v>
+        <v>32.458</v>
       </c>
       <c r="F29">
-        <v>3.142</v>
+        <v>3.109</v>
       </c>
       <c r="G29">
-        <v>2.397</v>
+        <v>2.373</v>
       </c>
       <c r="H29">
-        <v>3.979</v>
+        <v>3.945</v>
       </c>
       <c r="I29">
-        <v>2103882.493</v>
+        <v>2084753.343</v>
       </c>
       <c r="J29">
-        <v>1770348.571</v>
+        <v>1753924.836</v>
       </c>
       <c r="K29">
-        <v>2460756.717</v>
+        <v>2439746.072</v>
       </c>
       <c r="L29">
-        <v>418072.365</v>
+        <v>413679.652</v>
       </c>
       <c r="M29">
-        <v>318836.261</v>
+        <v>315199.613</v>
       </c>
       <c r="N29">
-        <v>529322.49</v>
+        <v>524482.7439999999</v>
       </c>
     </row>
     <row r="30">
@@ -1878,40 +1878,40 @@
         </is>
       </c>
       <c r="C32">
-        <v>162.64</v>
+        <v>164.73</v>
       </c>
       <c r="D32">
-        <v>147.163</v>
+        <v>149.002</v>
       </c>
       <c r="E32">
-        <v>178.509</v>
+        <v>180.734</v>
       </c>
       <c r="F32">
-        <v>1324.574</v>
+        <v>1341.11</v>
       </c>
       <c r="G32">
-        <v>1193.992</v>
+        <v>1209.463</v>
       </c>
       <c r="H32">
-        <v>1458.277</v>
+        <v>1476.19</v>
       </c>
       <c r="I32">
-        <v>2738838.345</v>
+        <v>2774058.828</v>
       </c>
       <c r="J32">
-        <v>2476963.059</v>
+        <v>2509598.851</v>
       </c>
       <c r="K32">
-        <v>3004999.044</v>
+        <v>3043616.113</v>
       </c>
       <c r="L32">
-        <v>176130220.716</v>
+        <v>178375751.523</v>
       </c>
       <c r="M32">
-        <v>158748435.972</v>
+        <v>160839236.238</v>
       </c>
       <c r="N32">
-        <v>194053867.538</v>
+        <v>196448873.004</v>
       </c>
     </row>
     <row r="33">
@@ -1926,40 +1926,40 @@
         </is>
       </c>
       <c r="C33">
-        <v>321.499</v>
+        <v>316.317</v>
       </c>
       <c r="D33">
-        <v>293.87</v>
+        <v>289.18</v>
       </c>
       <c r="E33">
-        <v>349.692</v>
+        <v>344.123</v>
       </c>
       <c r="F33">
-        <v>1912.759</v>
+        <v>1879.63</v>
       </c>
       <c r="G33">
-        <v>1744.743</v>
+        <v>1714.545</v>
       </c>
       <c r="H33">
-        <v>2084.882</v>
+        <v>2049.65</v>
       </c>
       <c r="I33">
-        <v>5414213.295</v>
+        <v>5325955.622</v>
       </c>
       <c r="J33">
-        <v>4949799.246</v>
+        <v>4869492.105</v>
       </c>
       <c r="K33">
-        <v>5886738.611</v>
+        <v>5793345.449</v>
       </c>
       <c r="L33">
-        <v>254374419.431</v>
+        <v>250010418.542</v>
       </c>
       <c r="M33">
-        <v>232044795.269</v>
+        <v>228131385.318</v>
       </c>
       <c r="N33">
-        <v>277283303.682</v>
+        <v>272499092.233</v>
       </c>
     </row>
     <row r="34">
@@ -1974,40 +1974,40 @@
         </is>
       </c>
       <c r="C34">
-        <v>1880.944</v>
+        <v>1891.863</v>
       </c>
       <c r="D34">
-        <v>1741.727</v>
+        <v>1751.498</v>
       </c>
       <c r="E34">
-        <v>2022.463</v>
+        <v>2034.149</v>
       </c>
       <c r="F34">
-        <v>7428.571</v>
+        <v>7475.165</v>
       </c>
       <c r="G34">
-        <v>6852.84</v>
+        <v>6898.115</v>
       </c>
       <c r="H34">
-        <v>8006.327</v>
+        <v>8058.477</v>
       </c>
       <c r="I34">
-        <v>31675589.924</v>
+        <v>31859543.28</v>
       </c>
       <c r="J34">
-        <v>29322580.703</v>
+        <v>29500794.537</v>
       </c>
       <c r="K34">
-        <v>34068213.539</v>
+        <v>34247475.308</v>
       </c>
       <c r="L34">
-        <v>987875281.286</v>
+        <v>994076425.516</v>
       </c>
       <c r="M34">
-        <v>911235268.645</v>
+        <v>917220419.7869999</v>
       </c>
       <c r="N34">
-        <v>1065330516.456</v>
+        <v>1071859877.368</v>
       </c>
     </row>
     <row r="35">
@@ -2022,40 +2022,40 @@
         </is>
       </c>
       <c r="C35">
-        <v>5144.545</v>
+        <v>5137.993</v>
       </c>
       <c r="D35">
-        <v>4727.5</v>
+        <v>4722.507</v>
       </c>
       <c r="E35">
-        <v>5567.344</v>
+        <v>5560.34</v>
       </c>
       <c r="F35">
-        <v>10439.692</v>
+        <v>10417.782</v>
       </c>
       <c r="G35">
-        <v>9482.368</v>
+        <v>9460.699000000001</v>
       </c>
       <c r="H35">
-        <v>11409.637</v>
+        <v>11381.575</v>
       </c>
       <c r="I35">
-        <v>86646881.733</v>
+        <v>86549201.09100001</v>
       </c>
       <c r="J35">
-        <v>79659715.65700001</v>
+        <v>79572009.75</v>
       </c>
       <c r="K35">
-        <v>93754962.52599999</v>
+        <v>93647094.228</v>
       </c>
       <c r="L35">
-        <v>1388583431.881</v>
+        <v>1385841726.218</v>
       </c>
       <c r="M35">
-        <v>1261388302.844</v>
+        <v>1258379709.382</v>
       </c>
       <c r="N35">
-        <v>1516629245.378</v>
+        <v>1514137048.275</v>
       </c>
     </row>
     <row r="36">
@@ -2070,40 +2070,40 @@
         </is>
       </c>
       <c r="C36">
-        <v>6421.702</v>
+        <v>6416.54</v>
       </c>
       <c r="D36">
-        <v>5678.141</v>
+        <v>5670.984</v>
       </c>
       <c r="E36">
-        <v>7179.698</v>
+        <v>7170.412</v>
       </c>
       <c r="F36">
-        <v>2131.272</v>
+        <v>2133.833</v>
       </c>
       <c r="G36">
-        <v>1739.501</v>
+        <v>1741.563</v>
       </c>
       <c r="H36">
-        <v>2530.787</v>
+        <v>2533.024</v>
       </c>
       <c r="I36">
-        <v>108186844.145</v>
+        <v>108069146.482</v>
       </c>
       <c r="J36">
-        <v>95590398.45900001</v>
+        <v>95534929.54700001</v>
       </c>
       <c r="K36">
-        <v>120925815.132</v>
+        <v>120787400.321</v>
       </c>
       <c r="L36">
-        <v>283372929.325</v>
+        <v>283727203.087</v>
       </c>
       <c r="M36">
-        <v>231344660.877</v>
+        <v>231628129.778</v>
       </c>
       <c r="N36">
-        <v>336814247.731</v>
+        <v>337104012.758</v>
       </c>
     </row>
     <row r="37">
@@ -2118,22 +2118,22 @@
         </is>
       </c>
       <c r="C37">
-        <v>23496.226</v>
+        <v>19049.559</v>
       </c>
       <c r="D37">
-        <v>20733.618</v>
+        <v>16725.041</v>
       </c>
       <c r="E37">
-        <v>26309.067</v>
+        <v>21477.241</v>
       </c>
       <c r="F37">
-        <v>2778.861</v>
+        <v>10742.403</v>
       </c>
       <c r="G37">
-        <v>2438.235</v>
+        <v>9357.040000000001</v>
       </c>
       <c r="H37">
-        <v>3134.895</v>
+        <v>12219.022</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -2145,13 +2145,13 @@
         <v>0</v>
       </c>
       <c r="L37">
-        <v>369570793.574</v>
+        <v>1428646781.76</v>
       </c>
       <c r="M37">
-        <v>324407482.31</v>
+        <v>1245206974.135</v>
       </c>
       <c r="N37">
-        <v>416890272.485</v>
+        <v>1626425157.257</v>
       </c>
     </row>
     <row r="38">
@@ -2166,22 +2166,22 @@
         </is>
       </c>
       <c r="C38">
-        <v>25297.87</v>
+        <v>20620.028</v>
       </c>
       <c r="D38">
-        <v>22503.604</v>
+        <v>18249.311</v>
       </c>
       <c r="E38">
-        <v>28112.47</v>
+        <v>23068.633</v>
       </c>
       <c r="F38">
-        <v>2990.535</v>
+        <v>9849.184999999999</v>
       </c>
       <c r="G38">
-        <v>2645.206</v>
+        <v>8647.174999999999</v>
       </c>
       <c r="H38">
-        <v>3348.112</v>
+        <v>11117.517</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -2193,13 +2193,13 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>397656058.842</v>
+        <v>1309554688.31</v>
       </c>
       <c r="M38">
-        <v>351720168.951</v>
+        <v>1151105908.347</v>
       </c>
       <c r="N38">
-        <v>444861351.913</v>
+        <v>1477609816.573</v>
       </c>
     </row>
     <row r="39">
@@ -2214,22 +2214,22 @@
         </is>
       </c>
       <c r="C39">
-        <v>24006.295</v>
+        <v>19795.069</v>
       </c>
       <c r="D39">
-        <v>21520.864</v>
+        <v>17668.761</v>
       </c>
       <c r="E39">
-        <v>26514.402</v>
+        <v>21971.639</v>
       </c>
       <c r="F39">
-        <v>2838.83</v>
+        <v>7828.191</v>
       </c>
       <c r="G39">
-        <v>2531.542</v>
+        <v>6913.931</v>
       </c>
       <c r="H39">
-        <v>3156.225</v>
+        <v>8784.995000000001</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -2241,13 +2241,13 @@
         <v>0</v>
       </c>
       <c r="L39">
-        <v>377638444.641</v>
+        <v>1041070652.669</v>
       </c>
       <c r="M39">
-        <v>336775006.812</v>
+        <v>919703757.3049999</v>
       </c>
       <c r="N39">
-        <v>419695850.26</v>
+        <v>1168201462.988</v>
       </c>
     </row>
     <row r="40">
@@ -2262,22 +2262,22 @@
         </is>
       </c>
       <c r="C40">
-        <v>23349.863</v>
+        <v>19524.186</v>
       </c>
       <c r="D40">
-        <v>21135.308</v>
+        <v>17617.39</v>
       </c>
       <c r="E40">
-        <v>25596.176</v>
+        <v>21474.985</v>
       </c>
       <c r="F40">
-        <v>2762.109</v>
+        <v>5816.455</v>
       </c>
       <c r="G40">
-        <v>2488.047</v>
+        <v>5201.819</v>
       </c>
       <c r="H40">
-        <v>3042.927</v>
+        <v>6460.125</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -2289,13 +2289,13 @@
         <v>0</v>
       </c>
       <c r="L40">
-        <v>367339698.078</v>
+        <v>773555251.494</v>
       </c>
       <c r="M40">
-        <v>331028451.795</v>
+        <v>692200650.456</v>
       </c>
       <c r="N40">
-        <v>404802567.323</v>
+        <v>858865890.441</v>
       </c>
     </row>
     <row r="41">
@@ -2310,22 +2310,22 @@
         </is>
       </c>
       <c r="C41">
-        <v>28405.421</v>
+        <v>23804.853</v>
       </c>
       <c r="D41">
-        <v>26112.666</v>
+        <v>21826.033</v>
       </c>
       <c r="E41">
-        <v>30707.416</v>
+        <v>25813.195</v>
       </c>
       <c r="F41">
-        <v>3360.027</v>
+        <v>4861.787</v>
       </c>
       <c r="G41">
-        <v>3075.819</v>
+        <v>4414.824</v>
       </c>
       <c r="H41">
-        <v>3649.886</v>
+        <v>5322.999</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -2337,13 +2337,13 @@
         <v>0</v>
       </c>
       <c r="L41">
-        <v>446808853.725</v>
+        <v>646596462.2819999</v>
       </c>
       <c r="M41">
-        <v>409100824.487</v>
+        <v>587325740.705</v>
       </c>
       <c r="N41">
-        <v>485261383.919</v>
+        <v>707629285.609</v>
       </c>
     </row>
     <row r="42">
@@ -2358,22 +2358,22 @@
         </is>
       </c>
       <c r="C42">
-        <v>19086.567</v>
+        <v>16054.274</v>
       </c>
       <c r="D42">
-        <v>17358.172</v>
+        <v>14562.38</v>
       </c>
       <c r="E42">
-        <v>20829.429</v>
+        <v>17573.134</v>
       </c>
       <c r="F42">
-        <v>2249.555</v>
+        <v>1768.212</v>
       </c>
       <c r="G42">
-        <v>2036.459</v>
+        <v>1571.439</v>
       </c>
       <c r="H42">
-        <v>2468.638</v>
+        <v>1973.523</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -2385,13 +2385,13 @@
         <v>0</v>
       </c>
       <c r="L42">
-        <v>299205409.541</v>
+        <v>235230691.543</v>
       </c>
       <c r="M42">
-        <v>270982668.105</v>
+        <v>209050200.293</v>
       </c>
       <c r="N42">
-        <v>328041214.407</v>
+        <v>262345801.189</v>
       </c>
     </row>
     <row r="43">
@@ -2406,22 +2406,22 @@
         </is>
       </c>
       <c r="C43">
-        <v>8263.718000000001</v>
+        <v>7114.52</v>
       </c>
       <c r="D43">
-        <v>7213.804</v>
+        <v>6193.65</v>
       </c>
       <c r="E43">
-        <v>9321.474</v>
+        <v>8059.037</v>
       </c>
       <c r="F43">
-        <v>524.409</v>
+        <v>143.901</v>
       </c>
       <c r="G43">
-        <v>429.522</v>
+        <v>114.769</v>
       </c>
       <c r="H43">
-        <v>623.777</v>
+        <v>174.732</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -2433,13 +2433,13 @@
         <v>0</v>
       </c>
       <c r="L43">
-        <v>69720704.037</v>
+        <v>19127733.449</v>
       </c>
       <c r="M43">
-        <v>57049396.848</v>
+        <v>15237633.967</v>
       </c>
       <c r="N43">
-        <v>82861488.765</v>
+        <v>23235438.301</v>
       </c>
     </row>
   </sheetData>
